--- a/SantanderCS/results/ResultListByTestModel_kjh.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_kjh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA95B079-1087-45CA-A079-E956F2D17D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE548C9-53C0-4BE3-A60A-9299943408E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
   <si>
     <t>NO</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -196,6 +196,208 @@
   </si>
   <si>
     <t>LightGBM_100_num31_min10_thr.pkl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    random_state      = 0,
+    n_estimators      = 100,
+    num_leaves        = 31,
+    min_child_samples = 10,
+    class_weight = {1:2},
+    Best Threshold: 0.26</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_100_num31_min10_class1vs2_thr.pkl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XGBoost HyperOpt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XGB_100_HP.pkl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  colsample_bytree: 0.6439821721137863
+  learning_rate: 0.12912822298301063
+  max_depth: 5
+  n_estimators: 250
+  subsample: 0.6974847094089329
+  random_state=42
+  Best Threshold: 0.15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  colsample_bytree: 0.6439821721137863
+  learning_rate: 0.12912822298301063
+  max_depth: 5
+  n_estimators: 250
+  subsample: 0.6974847094089329
+  random_state=42</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XGB_100_HP_thr_0.15.pkl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest HyperOpt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF_100_HP_max7_est350_classWeight1vs4.pkl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF_100_HP_max7_est350_classWeight1vs4_thr_0.17.pkl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM HyperOpt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LGBM_100_HP_lr0.5_max6_min17_est350_num16_class1vs4.pkl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{   'class_weight': {0: 1, 1: 4}, 
+    'colsample_bytree': 0.993915676646864, 
+    'learning_rate': 0.05861943746307052, 
+    'max_depth': 6, 
+    'min_child_samples': 17, 
+    'n_estimators': 350, 
+    'num_leaves': 16, 
+    'subsample': 0.6649208086751857 }</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{   'max_depth': 7, 
+    'max_features': 1, 
+    'min_samples_leaf': 3, 
+    'min_samples_split': 7, 
+    'n_estimators': 350, 
+    'class_weight': {0: 1, 1: 4} 
+    Best Threshold: 0.17 }</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{   'max_depth': 7, 
+    'max_features': 1, 
+    'min_samples_leaf': 3, 
+    'min_samples_split': 7, 
+    'n_estimators': 350, 
+    'class_weight': {0: 1, 1: 4} }</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{   'class_weight': {0: 1, 1: 4}, 
+    'colsample_bytree': 0.993915676646864, 
+    'learning_rate': 0.05861943746307052, 
+    'max_depth': 6, 
+    'min_child_samples': 17, 
+    'n_estimators': 350, 
+    'num_leaves': 16, 
+    'subsample': 0.6649208086751857
+    Best Threshold = 0.44 }</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LGBM_100_HP_lr0.5_max6_min17_est350_num16_class1vs4_thr_0.44.pkl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking_model = StackingClassifier(
+    estimators      = [
+        ("rf",   rf_clf),
+        ("xgb",  xgb_clf),
+        ("lgbm", lgbm_clf)
+    ],
+    final_estimator = meta_model,
+    cv              = StratifiedKFold(n_splits=5, shuffle=True, random_state=42),
+    stack_method    = "predict_proba",
+    n_jobs          = -1,
+    passthrough     = False
+)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stacking</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stacking_100_RF_XGB_LGBM_metaLR.pkl
+RF 기여도(계수): 0.9576
+XGB 기여도(계수): 1.9456
+LGBM 기여도(계수): 5.5153
+AUC       : 0.8481
+재현율    : 0.6728
+F1-score  : 0.2511</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled
+로그변환 x</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(60816, 86)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking_model_log = StackingClassifier(
+    estimators      = [
+        ("rf",   rf_clf_log),
+        ("xgb",  xgb_clf_log),
+        ("lgbm", lgbm_clf_log)
+    ],
+    final_estimator = meta_model_log,
+    cv              = StratifiedKFold(n_splits=5, shuffle=True, random_state=42),
+    stack_method    = "predict_proba",
+    n_jobs          = -1,
+    passthrough     = False
+)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled / log1p</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stacking_100_log1p_RF_XGB_LGBM_metaLR.pkl
+RF 기여도(계수): 0.9697
+XGB 기여도(계수): 1.9868
+LGBM 기여도(계수): 5.5184
+AUC       : 0.8491
+재현율    : 0.6777
+F1-score  : 0.2521</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking_model = StackingClassifier(
+    estimators      = [('rf', rf_clf), ('xgb', xgb_clf), ('lgbm', lgbm_clf)],
+    final_estimator = meta_model,
+    cv              = StratifiedKFold(n_splits=5, shuffle=True, random_state=42),
+    n_jobs          = -1
+)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled / 
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제 /</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackingModel_log1p_XGB_LGBM_RF_20251124.pkl
+RandomForest 기여도(계수): 8.3601
+XGBoost 기여도(계수): 7.1733
+LightGBM 기여도(계수): 3.8090
+Stacking 모델 ROC-AUC: 0.8465
+Stacking 모델 F1-Score: 0.2557
+Stacking 모델 Recall:   0.6262</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -416,7 +618,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -488,6 +690,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1094,7 +1299,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="99" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>7</v>
       </c>
@@ -1109,27 +1314,27 @@
         <v>13</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F10" s="23">
-        <v>0.84370000000000001</v>
+        <v>0.84560000000000002</v>
       </c>
       <c r="G10" s="13">
-        <v>1.9400000000000001E-2</v>
+        <v>0.29880000000000001</v>
       </c>
       <c r="H10" s="13">
-        <v>0.01</v>
+        <v>0.46010000000000001</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="99" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
         <v>7</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C11" s="13">
         <f>369</f>
@@ -1139,27 +1344,27 @@
         <v>13</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F11" s="23">
-        <v>0.84370000000000001</v>
+        <v>0.84279999999999999</v>
       </c>
       <c r="G11" s="13">
-        <v>1.9400000000000001E-2</v>
+        <v>3.5400000000000001E-2</v>
       </c>
       <c r="H11" s="13">
-        <v>0.01</v>
+        <v>1.83E-2</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
         <v>7</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C12" s="13">
         <f>369</f>
@@ -1169,27 +1374,27 @@
         <v>13</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F12" s="23">
-        <v>0.84370000000000001</v>
+        <v>0.84279999999999999</v>
       </c>
       <c r="G12" s="13">
-        <v>1.9400000000000001E-2</v>
+        <v>0.29459999999999997</v>
       </c>
       <c r="H12" s="13">
-        <v>0.01</v>
+        <v>0.45019999999999999</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="99" x14ac:dyDescent="0.3">
       <c r="A13" s="12">
         <v>7</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C13" s="13">
         <f>369</f>
@@ -1199,108 +1404,221 @@
         <v>13</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F13" s="23">
-        <v>0.84370000000000001</v>
+        <v>0.78369999999999995</v>
       </c>
       <c r="G13" s="13">
-        <v>1.9400000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="13">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="7"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
+        <v>7</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="13">
+        <f>369</f>
+        <v>369</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="23">
+        <v>0.78369999999999995</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0.24690000000000001</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0.55149999999999999</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
+        <v>7</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="13">
+        <f>369</f>
+        <v>369</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0.84750000000000003</v>
+      </c>
+      <c r="G15" s="13">
+        <v>0.25090000000000001</v>
+      </c>
+      <c r="H15" s="13">
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="12">
+        <v>7</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="13">
+        <f>369</f>
+        <v>369</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="23">
+        <v>0.78369999999999995</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0.30320000000000003</v>
+      </c>
+      <c r="H16" s="13">
+        <v>0.4153</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="214.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="12">
+        <v>7</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="13">
+        <f>369</f>
+        <v>369</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="23">
+        <v>0.84809999999999997</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0.25109999999999999</v>
+      </c>
+      <c r="H17" s="13">
+        <v>0.67279999999999995</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="214.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
+        <v>7</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="13">
+        <f>369</f>
+        <v>369</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="23">
+        <v>0.84909999999999997</v>
+      </c>
+      <c r="G18" s="13">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="H18" s="13">
+        <v>0.67769999999999997</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
+        <v>7</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="23">
+        <v>0.78369999999999995</v>
+      </c>
+      <c r="G19" s="13">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13">
+        <v>0</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="7"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="15"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="7"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
